--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484221_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484221_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6463</v>
+        <v>2.0591</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0165</v>
+        <v>0.2386</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6298</v>
+        <v>1.8205</v>
       </c>
       <c r="G2" t="n">
         <v>1.8255</v>
@@ -610,13 +610,13 @@
         <v>0.7814</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3709</v>
+        <v>0.0419</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3631</v>
+        <v>-0.141</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0077</v>
+        <v>0.1829</v>
       </c>
       <c r="V2" t="n">
         <v>0.3869</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5765</v>
+        <v>1.3415</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7087</v>
+        <v>0.3648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8678</v>
+        <v>0.9767</v>
       </c>
       <c r="G3" t="n">
         <v>0.6207</v>
@@ -688,13 +688,13 @@
         <v>0.3907</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5652</v>
+        <v>0.3302</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6274</v>
+        <v>0.2834</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0622</v>
+        <v>0.0467</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2486</v>
+        <v>1.3149</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4098</v>
+        <v>0.3685</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1612</v>
+        <v>0.9465</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.6722</v>
+        <v>1.0625</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1185</v>
+        <v>0.7524</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5537</v>
+        <v>0.3101</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2134</v>
+        <v>0.3884</v>
       </c>
       <c r="K4" t="n">
-        <v>0.092</v>
+        <v>0.3479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1214</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8856</v>
+        <v>0.6741</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2105</v>
+        <v>0.4045</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6751</v>
+        <v>0.2696</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>7.7029</v>
+        <v>0.0571</v>
       </c>
       <c r="T4" t="n">
-        <v>7.4593</v>
+        <v>-0.0199</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2435</v>
+        <v>0.077</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.438</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.1608</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2077</v>
+        <v>0.5221</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2068</v>
+        <v>1.5584</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0009</v>
+        <v>-1.0363</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0625</v>
+        <v>-1.7368</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7524</v>
+        <v>-1.5892</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3101</v>
+        <v>-0.1477</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3884</v>
+        <v>-0.289</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3479</v>
+        <v>-0.142</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>-0.1471</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6741</v>
+        <v>-1.4478</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4045</v>
+        <v>-1.4472</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2696</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0501</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1816</v>
+        <v>0.8242</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1315</v>
+        <v>-0.128</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0066</v>
+        <v>-0.5705</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2514</v>
+        <v>-1.202</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2579</v>
+        <v>0.6315</v>
       </c>
       <c r="G6" t="n">
         <v>-3.1876</v>
@@ -922,13 +922,13 @@
         <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6984</v>
+        <v>2.1213</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6664</v>
+        <v>1.7157</v>
       </c>
       <c r="U6" t="n">
-        <v>1.032</v>
+        <v>0.4056</v>
       </c>
       <c r="V6" t="n">
         <v>0.8865</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2537</v>
+        <v>-1.2005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0823</v>
+        <v>-1.9665</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3359</v>
+        <v>0.766</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7368</v>
+        <v>-1.1822</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5892</v>
+        <v>-0.5889</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1477</v>
+        <v>-0.5934</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.289</v>
+        <v>-1.0831</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.142</v>
+        <v>0.1842</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1471</v>
+        <v>-1.2673</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4478</v>
+        <v>-0.0992</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4472</v>
+        <v>-0.7731</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0796</v>
+        <v>-0.1354</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.652</v>
+        <v>-0.0239</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4276</v>
+        <v>-0.1116</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7273</v>
+        <v>-3.3055</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1393</v>
+        <v>-2.3735</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4119</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1822</v>
+        <v>-4.177</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5889</v>
+        <v>-2.8025</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5934</v>
+        <v>-1.3745</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0831</v>
+        <v>-2.7946</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1842</v>
+        <v>-1.2855</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2673</v>
+        <v>-1.5091</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0992</v>
+        <v>-1.3824</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7731</v>
+        <v>-1.517</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6623</v>
+        <v>0.2855</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1967</v>
+        <v>0.1439</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4656</v>
+        <v>0.1416</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5937</v>
+        <v>-3.4862</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7979</v>
+        <v>-2.0799</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7958</v>
+        <v>-1.4063</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.177</v>
+        <v>-2.6722</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8025</v>
+        <v>-2.1185</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3745</v>
+        <v>-0.5537</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7946</v>
+        <v>0.2134</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2855</v>
+        <v>0.092</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5091</v>
+        <v>0.1214</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3824</v>
+        <v>-2.8856</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.517</v>
+        <v>-2.2105</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1346</v>
+        <v>-0.6751</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.1022</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0027</v>
+        <v>2.9681</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2805</v>
+        <v>2.9697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2778</v>
+        <v>-0.0016</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.438</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>-1.1608</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2772</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4471</v>
+        <v>-5.1891</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.8126</v>
+        <v>-3.9981</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3655</v>
+        <v>-1.191</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3936</v>
+        <v>-4.5516</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.6089</v>
+        <v>-2.569</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2154</v>
+        <v>-1.9826</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2855</v>
+        <v>-2.285</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3664</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-1.3077</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1081</v>
+        <v>-2.2666</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2425</v>
+        <v>-1.5917</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1344</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2515</v>
+        <v>-0.1334</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5226</v>
+        <v>-0.0369</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7741</v>
+        <v>-0.0964</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3283</v>
+        <v>0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0511</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8347</v>
+        <v>-5.4989</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5348</v>
+        <v>-2.8625</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2999</v>
+        <v>-2.6364</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.5516</v>
+        <v>-5.3002</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.569</v>
+        <v>-3.4933</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9826</v>
+        <v>-1.8069</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.285</v>
+        <v>-2.21</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-0.8085</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3077</v>
+        <v>-1.4015</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2666</v>
+        <v>-3.0903</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5917</v>
+        <v>-2.6848</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.4054</v>
       </c>
       <c r="P11" t="n">
         <v>-0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.779</v>
+        <v>0.5827</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5736</v>
+        <v>0.8869</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2054</v>
+        <v>-0.3042</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3152</v>
+        <v>-5.5651</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3793</v>
+        <v>-5.631</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.936</v>
+        <v>0.0659</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3002</v>
+        <v>-3.3936</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.4933</v>
+        <v>-3.6089</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8069</v>
+        <v>0.2154</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.21</v>
+        <v>-2.2855</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8085</v>
+        <v>-2.3664</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4015</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0903</v>
+        <v>-1.1081</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.6848</v>
+        <v>-1.2425</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4054</v>
+        <v>0.1344</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2336</v>
+        <v>0.1335</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6299</v>
+        <v>-0.341</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6038</v>
+        <v>0.4745</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.3283</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6093</v>
+        <v>-1.0511</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.486</v>
+        <v>-19.5782</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.4912</v>
+        <v>-17.5832</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.995</v>
+        <v>-1.9949</v>
       </c>
       <c r="G13" t="n">
         <v>-22.6925</v>
@@ -1444,10 +1444,10 @@
         <v>-10.5632</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.5003</v>
+        <v>-4.500299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.063000000000001</v>
+        <v>-6.063000000000002</v>
       </c>
       <c r="M13" t="n">
         <v>-12.1296</v>
@@ -1456,7 +1456,7 @@
         <v>-12.1245</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.005100000000000104</v>
+        <v>-0.005099999999999966</v>
       </c>
       <c r="P13" t="n">
         <v>-1.9535</v>
@@ -1468,19 +1468,19 @@
         <v>11.7206</v>
       </c>
       <c r="S13" t="n">
-        <v>6.039800000000001</v>
+        <v>6.9476</v>
       </c>
       <c r="T13" t="n">
-        <v>5.3531</v>
+        <v>6.261099999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6866</v>
+        <v>0.6864999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8799</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3926999999999997</v>
+        <v>0.3926999999999998</v>
       </c>
       <c r="X13" t="n">
         <v>-2.2726</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4768</v>
+        <v>4.342</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1773</v>
+        <v>0.7729</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2995</v>
+        <v>3.5691</v>
       </c>
       <c r="G14" t="n">
         <v>2.4965</v>
@@ -1546,13 +1546,13 @@
         <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5201</v>
+        <v>-0.6549</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3936</v>
+        <v>-0.0108</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9137</v>
+        <v>-0.6441</v>
       </c>
       <c r="V14" t="n">
         <v>1.3283</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0768</v>
+        <v>4.0509</v>
       </c>
       <c r="E15" t="n">
-        <v>1.597</v>
+        <v>1.1925</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4798</v>
+        <v>2.8584</v>
       </c>
       <c r="G15" t="n">
         <v>3.2012</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2108</v>
+        <v>-0.2367</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4817</v>
+        <v>0.0772</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6925</v>
+        <v>-0.3139</v>
       </c>
       <c r="V15" t="n">
         <v>0.1097</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8761</v>
+        <v>3.9089</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6268</v>
+        <v>0.5557</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2494</v>
+        <v>3.3532</v>
       </c>
       <c r="G16" t="n">
-        <v>2.966</v>
+        <v>5.9706</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2901</v>
+        <v>2.9085</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3241</v>
+        <v>3.0622</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2566</v>
+        <v>4.1127</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8498</v>
+        <v>2.3983</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.7144</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7094</v>
+        <v>1.858</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4403</v>
+        <v>0.5102</v>
       </c>
       <c r="O16" t="n">
-        <v>0.269</v>
+        <v>1.3478</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3279</v>
+        <v>-0.4795</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3469</v>
+        <v>-0.2399</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.019</v>
+        <v>-0.2396</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3869</v>
+        <v>-0.9962</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3869</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9586</v>
+        <v>3.3536</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4031</v>
+        <v>1.3235</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5555</v>
+        <v>2.0301</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7236</v>
+        <v>2.966</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1576</v>
+        <v>3.2901</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5659</v>
+        <v>-0.3241</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1294</v>
+        <v>2.2566</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9675</v>
+        <v>2.8498</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1619</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5942</v>
+        <v>0.7094</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1901</v>
+        <v>0.4403</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>0.269</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0081</v>
+        <v>-0.1947</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2504</v>
+        <v>0.0435</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2423</v>
+        <v>-0.2382</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1638</v>
+        <v>0.3869</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1638</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6979</v>
+        <v>2.449</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0501</v>
+        <v>2.302</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6478</v>
+        <v>0.1469</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9706</v>
+        <v>3.7236</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9085</v>
+        <v>3.1576</v>
       </c>
       <c r="I18" t="n">
-        <v>3.0622</v>
+        <v>0.5659</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1127</v>
+        <v>3.1294</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3983</v>
+        <v>2.9675</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7144</v>
+        <v>0.1619</v>
       </c>
       <c r="M18" t="n">
-        <v>1.858</v>
+        <v>0.5942</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5102</v>
+        <v>0.1901</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3478</v>
+        <v>0.4041</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6905</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7455000000000001</v>
+        <v>0.1493</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.945</v>
+        <v>-0.6508</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9962</v>
+        <v>-1.1638</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8443</v>
+        <v>1.8021</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1167</v>
+        <v>-1.6802</v>
       </c>
       <c r="F19" t="n">
-        <v>1.961</v>
+        <v>3.4824</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3568</v>
+        <v>2.8835</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3564</v>
+        <v>2.2088</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0004</v>
+        <v>0.6747</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.3514</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>1.0246</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.6731</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2547</v>
+        <v>2.5321</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2551</v>
+        <v>1.1843</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0004</v>
+        <v>1.3478</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5601</v>
+        <v>-1.2767</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2175</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3427</v>
+        <v>-1.1985</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9762</v>
+        <v>1.432</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8825</v>
+        <v>-0.4201</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8587</v>
+        <v>1.8521</v>
       </c>
       <c r="G20" t="n">
-        <v>2.8835</v>
+        <v>-0.3568</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2088</v>
+        <v>-0.3564</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6747</v>
+        <v>-0.0004</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3514</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0246</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6731</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.5321</v>
+        <v>0.2547</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1843</v>
+        <v>0.2551</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3478</v>
+        <v>-0.0004</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1026</v>
+        <v>0.1479</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2805</v>
+        <v>-0.0859</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8222</v>
+        <v>0.2337</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8771</v>
+        <v>1.1182</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3625</v>
+        <v>0.7669</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5147</v>
+        <v>0.3513</v>
       </c>
       <c r="G21" t="n">
         <v>2.6687</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0335</v>
+        <v>-0.7924</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7125</v>
+        <v>-0.308</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.321</v>
+        <v>-0.4844</v>
       </c>
       <c r="V21" t="n">
         <v>0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2954</v>
+        <v>0.3499</v>
       </c>
       <c r="E22" t="n">
         <v>0.5382</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2428</v>
+        <v>-0.1884</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9733000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0501</v>
+        <v>0.1046</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0467</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0968</v>
+        <v>0.1513</v>
       </c>
       <c r="V22" t="n">
         <v>1.2186</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5932</v>
+        <v>-0.9722</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7609</v>
+        <v>-3.3565</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1677</v>
+        <v>2.3842</v>
       </c>
       <c r="G23" t="n">
         <v>0.1125</v>
@@ -2248,13 +2248,13 @@
         <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4285</v>
+        <v>-0.8076</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5915</v>
+        <v>-0.187</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8371</v>
+        <v>-0.6206</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2772</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>20.486</v>
+        <v>21.8344</v>
       </c>
       <c r="E24" t="n">
         <v>1.9949</v>
       </c>
       <c r="F24" t="n">
-        <v>18.4913</v>
+        <v>19.8393</v>
       </c>
       <c r="G24" t="n">
         <v>22.6925</v>
@@ -2296,7 +2296,7 @@
         <v>16.6247</v>
       </c>
       <c r="I24" t="n">
-        <v>6.067899999999999</v>
+        <v>6.0679</v>
       </c>
       <c r="J24" t="n">
         <v>12.1295</v>
@@ -2305,7 +2305,7 @@
         <v>12.1245</v>
       </c>
       <c r="L24" t="n">
-        <v>0.005000000000000129</v>
+        <v>0.004999999999999907</v>
       </c>
       <c r="M24" t="n">
         <v>10.5634</v>
@@ -2326,13 +2326,13 @@
         <v>13.674</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.0398</v>
+        <v>-4.6915</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6866000000000002</v>
+        <v>-0.6866000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.353299999999999</v>
+        <v>-4.005100000000001</v>
       </c>
       <c r="V24" t="n">
         <v>1.8798</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484221_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484221_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +653,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3415</v>
+        <v>1.521</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3648</v>
+        <v>1.521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6207</v>
+        <v>1.521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3106</v>
+        <v>0.307</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3101</v>
+        <v>1.214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0814</v>
+        <v>1.521</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0409</v>
+        <v>0.307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0405</v>
+        <v>1.214</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3302</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2834</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0467</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -704,12 +714,17 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +736,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3149</v>
+        <v>1.3415</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3685</v>
+        <v>0.3648</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9465</v>
+        <v>0.9767</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0625</v>
+        <v>0.6207</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7524</v>
+        <v>0.3106</v>
       </c>
       <c r="I4" t="n">
         <v>0.3101</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3884</v>
+        <v>0.0814</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3479</v>
+        <v>0.0409</v>
       </c>
       <c r="L4" t="n">
         <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6741</v>
+        <v>0.5393</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4045</v>
+        <v>0.2696</v>
       </c>
       <c r="O4" t="n">
         <v>0.2696</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0571</v>
+        <v>0.3302</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0199</v>
+        <v>0.2834</v>
       </c>
       <c r="U4" t="n">
-        <v>0.077</v>
+        <v>0.0467</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -782,12 +797,17 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +819,72 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5221</v>
+        <v>1.3149</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5584</v>
+        <v>0.3685</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0363</v>
+        <v>0.9465</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7368</v>
+        <v>1.0625</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5892</v>
+        <v>0.7524</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1477</v>
+        <v>0.3101</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.289</v>
+        <v>0.3884</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.142</v>
+        <v>0.3479</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1471</v>
+        <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4478</v>
+        <v>0.6741</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4472</v>
+        <v>0.4045</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.2696</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.0571</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8242</v>
+        <v>-0.0199</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.128</v>
+        <v>0.077</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2005</v>
+        <v>-0.9989</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9665</v>
+        <v>0.0374</v>
       </c>
       <c r="F7" t="n">
-        <v>0.766</v>
+        <v>-1.0363</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1822</v>
+        <v>-3.2578</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5889</v>
+        <v>-1.8961</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5934</v>
+        <v>-1.3616</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0831</v>
+        <v>-1.81</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1842</v>
+        <v>-0.449</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2673</v>
+        <v>-1.361</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0992</v>
+        <v>-1.4478</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7731</v>
+        <v>-1.4472</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1354</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0239</v>
+        <v>0.8242</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1116</v>
+        <v>-0.128</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3055</v>
+        <v>-1.2005</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3735</v>
+        <v>-1.9665</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.766</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.177</v>
+        <v>-1.1822</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8025</v>
+        <v>-0.5889</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3745</v>
+        <v>-0.5934</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7946</v>
+        <v>-1.0831</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2855</v>
+        <v>0.1842</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5091</v>
+        <v>-1.2673</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3824</v>
+        <v>-0.0992</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.517</v>
+        <v>-0.7731</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1346</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2855</v>
+        <v>-0.1354</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1439</v>
+        <v>-0.0239</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1416</v>
+        <v>-0.1116</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4862</v>
+        <v>-3.3055</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0799</v>
+        <v>-2.3735</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4063</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6722</v>
+        <v>-4.177</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1185</v>
+        <v>-2.8025</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5537</v>
+        <v>-1.3745</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2134</v>
+        <v>-2.7946</v>
       </c>
       <c r="K9" t="n">
-        <v>0.092</v>
+        <v>-1.2855</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1214</v>
+        <v>-1.5091</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8856</v>
+        <v>-1.3824</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2105</v>
+        <v>-1.517</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6751</v>
+        <v>0.1346</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9681</v>
+        <v>0.2855</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9697</v>
+        <v>0.1439</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0016</v>
+        <v>0.1416</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.438</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.1608</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1891</v>
+        <v>-3.4862</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9981</v>
+        <v>-2.0799</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.191</v>
+        <v>-1.4063</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.5516</v>
+        <v>-2.6722</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.569</v>
+        <v>-2.1185</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9826</v>
+        <v>-0.5537</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.285</v>
+        <v>0.2134</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9772999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3077</v>
+        <v>0.1214</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2666</v>
+        <v>-2.8856</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5917</v>
+        <v>-2.2105</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.6751</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-4.1022</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1334</v>
+        <v>2.9681</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0369</v>
+        <v>2.9697</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0964</v>
+        <v>-0.0016</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2772</v>
+        <v>-1.438</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>-1.1608</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4989</v>
+        <v>-5.1891</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8625</v>
+        <v>-3.9981</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6364</v>
+        <v>-1.191</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.3002</v>
+        <v>-4.5516</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4933</v>
+        <v>-2.569</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8069</v>
+        <v>-1.9826</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.21</v>
+        <v>-2.285</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8085</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4015</v>
+        <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0903</v>
+        <v>-2.2666</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.6848</v>
+        <v>-1.5917</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4054</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P11" t="n">
         <v>-0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5827</v>
+        <v>-0.1334</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8869</v>
+        <v>-0.0369</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3042</v>
+        <v>-0.0964</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5651</v>
+        <v>-5.4989</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.631</v>
+        <v>-2.8625</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0659</v>
+        <v>-2.6364</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3936</v>
+        <v>-5.3002</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.6089</v>
+        <v>-3.4933</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2154</v>
+        <v>-1.8069</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2855</v>
+        <v>-2.21</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.3664</v>
+        <v>-0.8085</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>-1.4015</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1081</v>
+        <v>-3.0903</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2425</v>
+        <v>-2.6848</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1344</v>
+        <v>-0.4054</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1335</v>
+        <v>0.5827</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.341</v>
+        <v>0.8869</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4745</v>
+        <v>-0.3042</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.0511</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.5782</v>
+        <v>-5.5651</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.5832</v>
+        <v>-5.631</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9949</v>
+        <v>0.0659</v>
       </c>
       <c r="G13" t="n">
-        <v>-22.6925</v>
+        <v>-3.3936</v>
       </c>
       <c r="H13" t="n">
-        <v>-16.6247</v>
+        <v>-3.6089</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0679</v>
+        <v>0.2154</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.5632</v>
+        <v>-2.2855</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.500299999999999</v>
+        <v>-2.3664</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.063000000000002</v>
+        <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.1296</v>
+        <v>-1.1081</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.1245</v>
+        <v>-1.2425</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.005099999999999966</v>
+        <v>0.1344</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.9535</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6739</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>11.7206</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>6.9476</v>
+        <v>0.1335</v>
       </c>
       <c r="T13" t="n">
-        <v>6.261099999999999</v>
+        <v>-0.341</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6864999999999999</v>
+        <v>0.4745</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8799</v>
+        <v>-1.3283</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3926999999999998</v>
+        <v>-1.0511</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2726</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.342</v>
+        <v>-19.5782</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7729</v>
+        <v>-17.5832</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5691</v>
+        <v>-1.9949</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4965</v>
+        <v>-22.6925</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4723</v>
+        <v>-16.6246</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0243</v>
+        <v>-6.0678</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2293</v>
+        <v>-10.5632</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1483</v>
+        <v>-4.5003</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0809</v>
+        <v>-6.062900000000003</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2673</v>
+        <v>-12.1296</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3239</v>
+        <v>-12.1245</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9433</v>
+        <v>-0.005100000000000188</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>-1.9535</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-13.6739</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>11.7206</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6549</v>
+        <v>6.9476</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0108</v>
+        <v>6.2611</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6441</v>
+        <v>0.6864999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3283</v>
+        <v>-1.8799</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>0.3926999999999996</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7739</v>
-      </c>
+        <v>-2.2726</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0509</v>
+        <v>4.342</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1925</v>
+        <v>0.7729</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8584</v>
+        <v>3.5691</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2012</v>
+        <v>2.4965</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3093</v>
+        <v>1.4723</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1082</v>
+        <v>1.0243</v>
       </c>
       <c r="J15" t="n">
-        <v>2.092</v>
+        <v>0.2293</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2783</v>
+        <v>0.1483</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1863</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1092</v>
+        <v>2.2673</v>
       </c>
       <c r="N15" t="n">
-        <v>0.031</v>
+        <v>1.3239</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0782</v>
+        <v>0.9433</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2367</v>
+        <v>-0.6549</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0772</v>
+        <v>-0.0108</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3139</v>
+        <v>-0.6441</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1097</v>
+        <v>1.3283</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1097</v>
+        <v>0.7739</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9089</v>
+        <v>4.0509</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5557</v>
+        <v>1.1925</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3532</v>
+        <v>2.8584</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9706</v>
+        <v>3.2012</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9085</v>
+        <v>3.3093</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0622</v>
+        <v>-0.1082</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1127</v>
+        <v>2.092</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3983</v>
+        <v>3.2783</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7144</v>
+        <v>-1.1863</v>
       </c>
       <c r="M16" t="n">
-        <v>1.858</v>
+        <v>1.1092</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5102</v>
+        <v>0.031</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3478</v>
+        <v>1.0782</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4795</v>
+        <v>-0.2367</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2399</v>
+        <v>0.0772</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2396</v>
+        <v>-0.3139</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9962</v>
+        <v>0.1097</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1811,72 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3536</v>
+        <v>3.9089</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3235</v>
+        <v>0.5557</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0301</v>
+        <v>3.3532</v>
       </c>
       <c r="G17" t="n">
-        <v>2.966</v>
+        <v>5.9706</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2901</v>
+        <v>2.9085</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3241</v>
+        <v>3.0622</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2566</v>
+        <v>4.1127</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8498</v>
+        <v>2.3983</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.7144</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7094</v>
+        <v>1.858</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4403</v>
+        <v>0.5102</v>
       </c>
       <c r="O17" t="n">
-        <v>0.269</v>
+        <v>1.3478</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1947</v>
+        <v>-0.4795</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0435</v>
+        <v>-0.2399</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2382</v>
+        <v>-0.2396</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3869</v>
+        <v>-0.9962</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3869</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1875,11 +1956,16 @@
       <c r="X18" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8021</v>
+        <v>2.4326</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6802</v>
+        <v>0.4025</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4824</v>
+        <v>2.0301</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8835</v>
+        <v>2.045</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2088</v>
+        <v>2.3692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6747</v>
+        <v>-0.3241</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3514</v>
+        <v>1.3357</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0246</v>
+        <v>1.9289</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6731</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5321</v>
+        <v>0.7094</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1843</v>
+        <v>0.4403</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3478</v>
+        <v>0.269</v>
       </c>
       <c r="P19" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2767</v>
+        <v>-0.1947</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0435</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1985</v>
+        <v>-0.2382</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.432</v>
+        <v>1.8021</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4201</v>
+        <v>-1.6802</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8521</v>
+        <v>3.4824</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3568</v>
+        <v>2.8835</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3564</v>
+        <v>2.2088</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0004</v>
+        <v>0.6747</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.3514</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6114000000000001</v>
+        <v>1.0246</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.6731</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2547</v>
+        <v>2.5321</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2551</v>
+        <v>1.1843</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0004</v>
+        <v>1.3478</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1479</v>
+        <v>-1.2767</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0859</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2337</v>
+        <v>-1.1985</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1182</v>
+        <v>1.432</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7669</v>
+        <v>-0.4201</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3513</v>
+        <v>1.8521</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6687</v>
+        <v>-0.3568</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6168</v>
+        <v>-0.3564</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0519</v>
+        <v>-0.0004</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4191</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2318</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1873</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2496</v>
+        <v>0.2547</v>
       </c>
       <c r="N21" t="n">
-        <v>0.385</v>
+        <v>0.2551</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>-0.0004</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7924</v>
+        <v>0.1479</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.308</v>
+        <v>-0.0859</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4844</v>
+        <v>0.2337</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6093</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3499</v>
+        <v>1.1182</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5382</v>
+        <v>0.7669</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1884</v>
+        <v>0.3513</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9733000000000001</v>
+        <v>2.6687</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0698</v>
+        <v>1.6168</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9035</v>
+        <v>1.0519</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>2.4191</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.2318</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.1873</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3397</v>
+        <v>0.2496</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0698</v>
+        <v>0.385</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2698</v>
+        <v>-0.1354</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1046</v>
+        <v>-0.7924</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0467</v>
+        <v>-0.308</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1513</v>
+        <v>-0.4844</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9722</v>
+        <v>0.921</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3565</v>
+        <v>0.921</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3842</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1125</v>
+        <v>0.921</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9125</v>
+        <v>0.921</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0251</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.216</v>
+        <v>0.921</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1627</v>
+        <v>0.921</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3286</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2502</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.0784</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8076</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.187</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6206</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5382</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.9733000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.9035</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.3397</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0467</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D. YUSTE MALO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.9722</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.3565</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.3842</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.9125</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.0251</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.216</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.1627</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.0533</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.3286</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.0784</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.8076</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.187</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.6206</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484221_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>21.8344</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>1.9949</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>19.8393</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>22.6925</v>
       </c>
-      <c r="H24" t="n">
-        <v>16.6247</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H26" t="n">
+        <v>16.6248</v>
+      </c>
+      <c r="I26" t="n">
         <v>6.0679</v>
       </c>
-      <c r="J24" t="n">
-        <v>12.1295</v>
-      </c>
-      <c r="K24" t="n">
-        <v>12.1245</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="J26" t="n">
+        <v>12.1296</v>
+      </c>
+      <c r="K26" t="n">
+        <v>12.1246</v>
+      </c>
+      <c r="L26" t="n">
         <v>0.004999999999999907</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>10.5634</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>4.500300000000001</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>6.063000000000001</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>1.9534</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>13.674</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>-4.6915</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-0.6866000000000001</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>-4.005100000000001</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.8798</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="V26" t="n">
+        <v>1.879799999999999</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.2727</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-0.3928999999999998</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
